--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127103007</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127102976</v>
       </c>
       <c r="B4" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127103032</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127102997</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127102977</v>
       </c>
       <c r="B7" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127103035</v>
       </c>
       <c r="B8" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127103002</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127102999</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127103031</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127094164</v>
+        <v>127102965</v>
       </c>
       <c r="B13" t="n">
         <v>57657</v>
@@ -1791,21 +1791,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591990</v>
+        <v>591937</v>
       </c>
       <c r="R13" t="n">
-        <v>6984385</v>
+        <v>6984488</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1837,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både äldre och färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,7 +1864,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127102965</v>
+        <v>127094164</v>
       </c>
       <c r="B14" t="n">
         <v>57657</v>
@@ -1898,16 +1893,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591937</v>
+        <v>591990</v>
       </c>
       <c r="R14" t="n">
-        <v>6984488</v>
+        <v>6984385</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127103008</v>
+        <v>127103000</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>591961</v>
+        <v>591887</v>
       </c>
       <c r="R15" t="n">
-        <v>6984476</v>
+        <v>6984545</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127103000</v>
+        <v>127103008</v>
       </c>
       <c r="B16" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>591887</v>
+        <v>591961</v>
       </c>
       <c r="R16" t="n">
-        <v>6984545</v>
+        <v>6984476</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,10 +2165,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127102974</v>
+        <v>127102975</v>
       </c>
       <c r="B17" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591910</v>
+        <v>591943</v>
       </c>
       <c r="R17" t="n">
-        <v>6984531</v>
+        <v>6984493</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102975</v>
+        <v>127102974</v>
       </c>
       <c r="B18" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591943</v>
+        <v>591910</v>
       </c>
       <c r="R18" t="n">
-        <v>6984493</v>
+        <v>6984531</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
         <v>127103001</v>
       </c>
       <c r="B20" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127103003</v>
       </c>
       <c r="B21" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127103007</v>
       </c>
       <c r="B3" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127102976</v>
+        <v>127103032</v>
       </c>
       <c r="B4" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591950</v>
+        <v>592024</v>
       </c>
       <c r="R4" t="n">
-        <v>6984488</v>
+        <v>6984409</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103032</v>
+        <v>127102976</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592024</v>
+        <v>591950</v>
       </c>
       <c r="R5" t="n">
-        <v>6984409</v>
+        <v>6984488</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
         <v>127102997</v>
       </c>
       <c r="B6" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127102977</v>
       </c>
       <c r="B7" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127103035</v>
       </c>
       <c r="B8" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127103002</v>
       </c>
       <c r="B9" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127102999</v>
       </c>
       <c r="B10" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127103031</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127102965</v>
+        <v>127094164</v>
       </c>
       <c r="B13" t="n">
         <v>57657</v>
@@ -1791,16 +1791,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591937</v>
+        <v>591990</v>
       </c>
       <c r="R13" t="n">
-        <v>6984488</v>
+        <v>6984385</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,7 +1842,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,7 +1869,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127094164</v>
+        <v>127102965</v>
       </c>
       <c r="B14" t="n">
         <v>57657</v>
@@ -1893,21 +1898,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591990</v>
+        <v>591937</v>
       </c>
       <c r="R14" t="n">
-        <v>6984385</v>
+        <v>6984488</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både äldre och färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,7 +1974,7 @@
         <v>127103000</v>
       </c>
       <c r="B15" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>127103008</v>
       </c>
       <c r="B16" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127102975</v>
+        <v>127102974</v>
       </c>
       <c r="B17" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591943</v>
+        <v>591910</v>
       </c>
       <c r="R17" t="n">
-        <v>6984493</v>
+        <v>6984531</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102974</v>
+        <v>127102975</v>
       </c>
       <c r="B18" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591910</v>
+        <v>591943</v>
       </c>
       <c r="R18" t="n">
-        <v>6984531</v>
+        <v>6984493</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
         <v>127103001</v>
       </c>
       <c r="B20" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127103003</v>
       </c>
       <c r="B21" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127095097</v>
+        <v>127103007</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591955</v>
+        <v>591953</v>
       </c>
       <c r="R2" t="n">
-        <v>6984372</v>
+        <v>6984486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127103007</v>
+        <v>127095097</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591953</v>
+        <v>591955</v>
       </c>
       <c r="R3" t="n">
-        <v>6984486</v>
+        <v>6984372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103032</v>
+        <v>127102976</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592024</v>
+        <v>591950</v>
       </c>
       <c r="R4" t="n">
-        <v>6984409</v>
+        <v>6984488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127102976</v>
+        <v>127103032</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591950</v>
+        <v>592024</v>
       </c>
       <c r="R5" t="n">
-        <v>6984488</v>
+        <v>6984409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127102974</v>
+        <v>127102975</v>
       </c>
       <c r="B17" t="n">
         <v>80146</v>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591910</v>
+        <v>591943</v>
       </c>
       <c r="R17" t="n">
-        <v>6984531</v>
+        <v>6984493</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102975</v>
+        <v>127102974</v>
       </c>
       <c r="B18" t="n">
         <v>80146</v>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591943</v>
+        <v>591910</v>
       </c>
       <c r="R18" t="n">
-        <v>6984493</v>
+        <v>6984531</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127094164</v>
+        <v>127102965</v>
       </c>
       <c r="B13" t="n">
         <v>57657</v>
@@ -1791,21 +1791,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591990</v>
+        <v>591937</v>
       </c>
       <c r="R13" t="n">
-        <v>6984385</v>
+        <v>6984488</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1837,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både äldre och färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,7 +1864,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127102965</v>
+        <v>127094164</v>
       </c>
       <c r="B14" t="n">
         <v>57657</v>
@@ -1898,16 +1893,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591937</v>
+        <v>591990</v>
       </c>
       <c r="R14" t="n">
-        <v>6984488</v>
+        <v>6984385</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127103007</v>
+        <v>127095097</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591953</v>
+        <v>591955</v>
       </c>
       <c r="R2" t="n">
-        <v>6984486</v>
+        <v>6984372</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127095097</v>
+        <v>127103007</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591955</v>
+        <v>591953</v>
       </c>
       <c r="R3" t="n">
-        <v>6984372</v>
+        <v>6984486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1270,7 +1270,7 @@
         <v>127103035</v>
       </c>
       <c r="B8" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2765,6 +2765,1093 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127405560</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92023</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>592002</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6984465</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127406047</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>592060</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6984421</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127405943</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>592043</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6984443</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack gran, både färska och gamla</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127405968</v>
+      </c>
+      <c r="B26" t="n">
+        <v>105478</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>592050</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6984433</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127406727</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56849</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>591958</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6984415</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127405894</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80153</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>592043</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6984443</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127406825</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>591928</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6984491</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127406344</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>592062</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6984382</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127406956</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>591868</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6984472</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127406007</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91780</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>592065</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6984424</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127406264</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98441</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>620</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Skogsfru</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Epipogium aphyllum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>592066</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6984408</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127102965</v>
+        <v>127094164</v>
       </c>
       <c r="B13" t="n">
         <v>57657</v>
@@ -1791,16 +1791,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591937</v>
+        <v>591990</v>
       </c>
       <c r="R13" t="n">
-        <v>6984488</v>
+        <v>6984385</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,7 +1842,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,7 +1869,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127094164</v>
+        <v>127102965</v>
       </c>
       <c r="B14" t="n">
         <v>57657</v>
@@ -1893,21 +1898,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591990</v>
+        <v>591937</v>
       </c>
       <c r="R14" t="n">
-        <v>6984385</v>
+        <v>6984488</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både äldre och färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127405968</v>
+        <v>127406727</v>
       </c>
       <c r="B26" t="n">
-        <v>105478</v>
+        <v>56849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,34 +3079,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592050</v>
+        <v>591958</v>
       </c>
       <c r="R26" t="n">
-        <v>6984433</v>
+        <v>6984415</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3165,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127406727</v>
+        <v>127405968</v>
       </c>
       <c r="B27" t="n">
-        <v>56849</v>
+        <v>105478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3176,39 +3181,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591958</v>
+        <v>592050</v>
       </c>
       <c r="R27" t="n">
-        <v>6984415</v>
+        <v>6984433</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127095097</v>
+        <v>127103007</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591955</v>
+        <v>591953</v>
       </c>
       <c r="R2" t="n">
-        <v>6984372</v>
+        <v>6984486</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127103007</v>
+        <v>127095097</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591953</v>
+        <v>591955</v>
       </c>
       <c r="R3" t="n">
-        <v>6984486</v>
+        <v>6984372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -3364,7 +3364,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127406825</v>
+        <v>127406956</v>
       </c>
       <c r="B29" t="n">
         <v>79014</v>
@@ -3395,14 +3395,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591928</v>
+        <v>591868</v>
       </c>
       <c r="R29" t="n">
-        <v>6984491</v>
+        <v>6984472</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3461,32 +3461,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127406344</v>
+        <v>127406007</v>
       </c>
       <c r="B30" t="n">
-        <v>91326</v>
+        <v>91780</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592062</v>
+        <v>592065</v>
       </c>
       <c r="R30" t="n">
-        <v>6984382</v>
+        <v>6984424</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406956</v>
+        <v>127406344</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>91326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591868</v>
+        <v>592062</v>
       </c>
       <c r="R31" t="n">
-        <v>6984472</v>
+        <v>6984382</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,32 +3655,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406007</v>
+        <v>127406825</v>
       </c>
       <c r="B32" t="n">
-        <v>91780</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592065</v>
+        <v>591928</v>
       </c>
       <c r="R32" t="n">
-        <v>6984424</v>
+        <v>6984491</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127103007</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127095097</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127102976</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127103032</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127102997</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127102977</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127103035</v>
       </c>
       <c r="B8" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127103002</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127102999</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127094740</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127103031</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127094164</v>
+        <v>127102965</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1791,21 +1791,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591990</v>
+        <v>591937</v>
       </c>
       <c r="R13" t="n">
-        <v>6984385</v>
+        <v>6984488</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1837,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både äldre och färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,10 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127102965</v>
+        <v>127094164</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,16 +1893,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591937</v>
+        <v>591990</v>
       </c>
       <c r="R14" t="n">
-        <v>6984488</v>
+        <v>6984385</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,7 +1974,7 @@
         <v>127103000</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>127103008</v>
       </c>
       <c r="B16" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>127102975</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>127102974</v>
       </c>
       <c r="B18" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>127094909</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>127103001</v>
       </c>
       <c r="B20" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127103003</v>
       </c>
       <c r="B21" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127094311</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127405560</v>
       </c>
       <c r="B23" t="n">
-        <v>92023</v>
+        <v>92027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127406047</v>
       </c>
       <c r="B24" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>127405943</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>127406727</v>
       </c>
       <c r="B26" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>127405968</v>
       </c>
       <c r="B27" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>127405894</v>
       </c>
       <c r="B28" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,45 +3364,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127406956</v>
+        <v>127406007</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>91784</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591868</v>
+        <v>592065</v>
       </c>
       <c r="R29" t="n">
-        <v>6984472</v>
+        <v>6984424</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3461,32 +3461,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127406007</v>
+        <v>127406344</v>
       </c>
       <c r="B30" t="n">
-        <v>91780</v>
+        <v>91330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592065</v>
+        <v>592062</v>
       </c>
       <c r="R30" t="n">
-        <v>6984424</v>
+        <v>6984382</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406344</v>
+        <v>127406825</v>
       </c>
       <c r="B31" t="n">
-        <v>91326</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592062</v>
+        <v>591928</v>
       </c>
       <c r="R31" t="n">
-        <v>6984382</v>
+        <v>6984491</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406825</v>
+        <v>127406956</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,14 +3686,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591928</v>
+        <v>591868</v>
       </c>
       <c r="R32" t="n">
-        <v>6984491</v>
+        <v>6984472</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>127406264</v>
       </c>
       <c r="B33" t="n">
-        <v>98441</v>
+        <v>98445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -3364,32 +3364,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127406007</v>
+        <v>127406825</v>
       </c>
       <c r="B29" t="n">
-        <v>91784</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592065</v>
+        <v>591928</v>
       </c>
       <c r="R29" t="n">
-        <v>6984424</v>
+        <v>6984491</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127406344</v>
+        <v>127406956</v>
       </c>
       <c r="B30" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3472,34 +3472,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592062</v>
+        <v>591868</v>
       </c>
       <c r="R30" t="n">
-        <v>6984382</v>
+        <v>6984472</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3558,32 +3558,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406825</v>
+        <v>127406007</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>91784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591928</v>
+        <v>592065</v>
       </c>
       <c r="R31" t="n">
-        <v>6984491</v>
+        <v>6984424</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406956</v>
+        <v>127406344</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591868</v>
+        <v>592062</v>
       </c>
       <c r="R32" t="n">
-        <v>6984472</v>
+        <v>6984382</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -3364,32 +3364,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127406825</v>
+        <v>127406007</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>91784</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591928</v>
+        <v>592065</v>
       </c>
       <c r="R29" t="n">
-        <v>6984491</v>
+        <v>6984424</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127406956</v>
+        <v>127406344</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3472,34 +3472,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591868</v>
+        <v>592062</v>
       </c>
       <c r="R30" t="n">
-        <v>6984472</v>
+        <v>6984382</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3558,32 +3558,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406007</v>
+        <v>127406825</v>
       </c>
       <c r="B31" t="n">
-        <v>91784</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592065</v>
+        <v>591928</v>
       </c>
       <c r="R31" t="n">
-        <v>6984424</v>
+        <v>6984491</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406344</v>
+        <v>127406956</v>
       </c>
       <c r="B32" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592062</v>
+        <v>591868</v>
       </c>
       <c r="R32" t="n">
-        <v>6984382</v>
+        <v>6984472</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127103007</v>
+        <v>127095097</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591953</v>
+        <v>591955</v>
       </c>
       <c r="R2" t="n">
-        <v>6984486</v>
+        <v>6984372</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127095097</v>
+        <v>127103007</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591955</v>
+        <v>591953</v>
       </c>
       <c r="R3" t="n">
-        <v>6984372</v>
+        <v>6984486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1270,7 +1270,7 @@
         <v>127103035</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127102975</v>
+        <v>127102974</v>
       </c>
       <c r="B17" t="n">
         <v>80150</v>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591943</v>
+        <v>591910</v>
       </c>
       <c r="R17" t="n">
-        <v>6984493</v>
+        <v>6984531</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102974</v>
+        <v>127102975</v>
       </c>
       <c r="B18" t="n">
         <v>80150</v>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591910</v>
+        <v>591943</v>
       </c>
       <c r="R18" t="n">
-        <v>6984531</v>
+        <v>6984493</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127406727</v>
+        <v>127405968</v>
       </c>
       <c r="B26" t="n">
-        <v>56853</v>
+        <v>105486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,39 +3079,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591958</v>
+        <v>592050</v>
       </c>
       <c r="R26" t="n">
-        <v>6984415</v>
+        <v>6984433</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3170,10 +3165,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127405968</v>
+        <v>127406727</v>
       </c>
       <c r="B27" t="n">
-        <v>105484</v>
+        <v>56853</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3181,34 +3176,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592050</v>
+        <v>591958</v>
       </c>
       <c r="R27" t="n">
-        <v>6984433</v>
+        <v>6984415</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3364,32 +3364,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127406825</v>
+        <v>127406007</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>91784</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591928</v>
+        <v>592065</v>
       </c>
       <c r="R29" t="n">
-        <v>6984491</v>
+        <v>6984424</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127406956</v>
+        <v>127406344</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3472,34 +3472,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591868</v>
+        <v>592062</v>
       </c>
       <c r="R30" t="n">
-        <v>6984472</v>
+        <v>6984382</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3558,32 +3558,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406007</v>
+        <v>127406825</v>
       </c>
       <c r="B31" t="n">
-        <v>91784</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592065</v>
+        <v>591928</v>
       </c>
       <c r="R31" t="n">
-        <v>6984424</v>
+        <v>6984491</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406344</v>
+        <v>127406956</v>
       </c>
       <c r="B32" t="n">
-        <v>91330</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592062</v>
+        <v>591868</v>
       </c>
       <c r="R32" t="n">
-        <v>6984382</v>
+        <v>6984472</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>127406264</v>
       </c>
       <c r="B33" t="n">
-        <v>98445</v>
+        <v>98446</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127405968</v>
+        <v>127406727</v>
       </c>
       <c r="B26" t="n">
-        <v>105486</v>
+        <v>56853</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,34 +3079,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592050</v>
+        <v>591958</v>
       </c>
       <c r="R26" t="n">
-        <v>6984433</v>
+        <v>6984415</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3165,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127406727</v>
+        <v>127405968</v>
       </c>
       <c r="B27" t="n">
-        <v>56853</v>
+        <v>105486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3176,39 +3181,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591958</v>
+        <v>592050</v>
       </c>
       <c r="R27" t="n">
-        <v>6984415</v>
+        <v>6984433</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127095097</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127103007</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127102976</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127103032</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127102997</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127102977</v>
       </c>
       <c r="B7" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127103035</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127103002</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127102999</v>
       </c>
       <c r="B10" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127094740</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127103031</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127102965</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>127094164</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>127103000</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>127103008</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127102974</v>
+        <v>127102975</v>
       </c>
       <c r="B17" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591910</v>
+        <v>591943</v>
       </c>
       <c r="R17" t="n">
-        <v>6984531</v>
+        <v>6984493</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,10 +2262,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102975</v>
+        <v>127102974</v>
       </c>
       <c r="B18" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591943</v>
+        <v>591910</v>
       </c>
       <c r="R18" t="n">
-        <v>6984493</v>
+        <v>6984531</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
         <v>127094909</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>127103001</v>
       </c>
       <c r="B20" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127103003</v>
       </c>
       <c r="B21" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127094311</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127405560</v>
       </c>
       <c r="B23" t="n">
-        <v>92027</v>
+        <v>92029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127406047</v>
       </c>
       <c r="B24" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>127405943</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127406727</v>
+        <v>127405968</v>
       </c>
       <c r="B26" t="n">
-        <v>56853</v>
+        <v>105488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,39 +3079,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591958</v>
+        <v>592050</v>
       </c>
       <c r="R26" t="n">
-        <v>6984415</v>
+        <v>6984433</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3170,10 +3165,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127405968</v>
+        <v>127406727</v>
       </c>
       <c r="B27" t="n">
-        <v>105486</v>
+        <v>56855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3181,34 +3176,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592050</v>
+        <v>591958</v>
       </c>
       <c r="R27" t="n">
-        <v>6984433</v>
+        <v>6984415</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3270,7 +3270,7 @@
         <v>127405894</v>
       </c>
       <c r="B28" t="n">
-        <v>80157</v>
+        <v>80159</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>127406007</v>
       </c>
       <c r="B29" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>127406344</v>
       </c>
       <c r="B30" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406825</v>
+        <v>127406956</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,14 +3589,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591928</v>
+        <v>591868</v>
       </c>
       <c r="R31" t="n">
-        <v>6984491</v>
+        <v>6984472</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406956</v>
+        <v>127406825</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,14 +3686,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591868</v>
+        <v>591928</v>
       </c>
       <c r="R32" t="n">
-        <v>6984472</v>
+        <v>6984491</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>127406264</v>
       </c>
       <c r="B33" t="n">
-        <v>98446</v>
+        <v>98448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127102976</v>
+        <v>127103032</v>
       </c>
       <c r="B4" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591950</v>
+        <v>592024</v>
       </c>
       <c r="R4" t="n">
-        <v>6984488</v>
+        <v>6984409</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103032</v>
+        <v>127102976</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>80152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592024</v>
+        <v>591950</v>
       </c>
       <c r="R5" t="n">
-        <v>6984409</v>
+        <v>6984488</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127102965</v>
+        <v>127094164</v>
       </c>
       <c r="B13" t="n">
         <v>57663</v>
@@ -1791,16 +1791,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591937</v>
+        <v>591990</v>
       </c>
       <c r="R13" t="n">
-        <v>6984488</v>
+        <v>6984385</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,7 +1842,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,7 +1869,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127094164</v>
+        <v>127102965</v>
       </c>
       <c r="B14" t="n">
         <v>57663</v>
@@ -1893,21 +1898,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591990</v>
+        <v>591937</v>
       </c>
       <c r="R14" t="n">
-        <v>6984385</v>
+        <v>6984488</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både äldre och färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127405968</v>
+        <v>127406727</v>
       </c>
       <c r="B26" t="n">
-        <v>105488</v>
+        <v>56855</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,34 +3079,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592050</v>
+        <v>591958</v>
       </c>
       <c r="R26" t="n">
-        <v>6984433</v>
+        <v>6984415</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3165,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127406727</v>
+        <v>127405968</v>
       </c>
       <c r="B27" t="n">
-        <v>56855</v>
+        <v>105488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3176,39 +3181,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591958</v>
+        <v>592050</v>
       </c>
       <c r="R27" t="n">
-        <v>6984415</v>
+        <v>6984433</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406956</v>
+        <v>127406825</v>
       </c>
       <c r="B31" t="n">
         <v>79020</v>
@@ -3589,14 +3589,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591868</v>
+        <v>591928</v>
       </c>
       <c r="R31" t="n">
-        <v>6984472</v>
+        <v>6984491</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,7 +3655,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406825</v>
+        <v>127406956</v>
       </c>
       <c r="B32" t="n">
         <v>79020</v>
@@ -3686,14 +3686,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591928</v>
+        <v>591868</v>
       </c>
       <c r="R32" t="n">
-        <v>6984491</v>
+        <v>6984472</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103032</v>
+        <v>127102976</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>80152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592024</v>
+        <v>591950</v>
       </c>
       <c r="R4" t="n">
-        <v>6984409</v>
+        <v>6984488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127102976</v>
+        <v>127103032</v>
       </c>
       <c r="B5" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591950</v>
+        <v>592024</v>
       </c>
       <c r="R5" t="n">
-        <v>6984488</v>
+        <v>6984409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127094164</v>
+        <v>127102965</v>
       </c>
       <c r="B13" t="n">
         <v>57663</v>
@@ -1791,21 +1791,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591990</v>
+        <v>591937</v>
       </c>
       <c r="R13" t="n">
-        <v>6984385</v>
+        <v>6984488</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1837,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både äldre och färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,7 +1864,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127102965</v>
+        <v>127094164</v>
       </c>
       <c r="B14" t="n">
         <v>57663</v>
@@ -1898,16 +1893,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591937</v>
+        <v>591990</v>
       </c>
       <c r="R14" t="n">
-        <v>6984488</v>
+        <v>6984385</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2165,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127102975</v>
+        <v>127102974</v>
       </c>
       <c r="B17" t="n">
         <v>80152</v>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591943</v>
+        <v>591910</v>
       </c>
       <c r="R17" t="n">
-        <v>6984493</v>
+        <v>6984531</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102974</v>
+        <v>127102975</v>
       </c>
       <c r="B18" t="n">
         <v>80152</v>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591910</v>
+        <v>591943</v>
       </c>
       <c r="R18" t="n">
-        <v>6984531</v>
+        <v>6984493</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -1270,7 +1270,7 @@
         <v>127103035</v>
       </c>
       <c r="B8" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127102965</v>
+        <v>127094164</v>
       </c>
       <c r="B13" t="n">
         <v>57663</v>
@@ -1791,16 +1791,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>591937</v>
+        <v>591990</v>
       </c>
       <c r="R13" t="n">
-        <v>6984488</v>
+        <v>6984385</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1837,7 +1842,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1864,7 +1869,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127094164</v>
+        <v>127102965</v>
       </c>
       <c r="B14" t="n">
         <v>57663</v>
@@ -1893,21 +1898,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>591990</v>
+        <v>591937</v>
       </c>
       <c r="R14" t="n">
-        <v>6984385</v>
+        <v>6984488</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både äldre och färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2165,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127102974</v>
+        <v>127102975</v>
       </c>
       <c r="B17" t="n">
         <v>80152</v>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>591910</v>
+        <v>591943</v>
       </c>
       <c r="R17" t="n">
-        <v>6984531</v>
+        <v>6984493</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127102975</v>
+        <v>127102974</v>
       </c>
       <c r="B18" t="n">
         <v>80152</v>
@@ -2297,10 +2297,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>591943</v>
+        <v>591910</v>
       </c>
       <c r="R18" t="n">
-        <v>6984493</v>
+        <v>6984531</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2770,7 +2770,7 @@
         <v>127405560</v>
       </c>
       <c r="B23" t="n">
-        <v>92029</v>
+        <v>92035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127406047</v>
       </c>
       <c r="B24" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>127405968</v>
       </c>
       <c r="B27" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>127406007</v>
       </c>
       <c r="B29" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>127406344</v>
       </c>
       <c r="B30" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>127406264</v>
       </c>
       <c r="B33" t="n">
-        <v>98448</v>
+        <v>98454</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127095097</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127103007</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127102976</v>
       </c>
       <c r="B4" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127103032</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127102997</v>
       </c>
       <c r="B6" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127102977</v>
       </c>
       <c r="B7" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127103035</v>
       </c>
       <c r="B8" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127103002</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127102999</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127094740</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127103031</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127094164</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>127102965</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>127103000</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>127103008</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>127102975</v>
       </c>
       <c r="B17" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>127102974</v>
       </c>
       <c r="B18" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>127094909</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>127103001</v>
       </c>
       <c r="B20" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127103003</v>
       </c>
       <c r="B21" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127094311</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127405560</v>
       </c>
       <c r="B23" t="n">
-        <v>92035</v>
+        <v>92038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127406047</v>
       </c>
       <c r="B24" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>127405943</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>127406727</v>
       </c>
       <c r="B26" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>127405968</v>
       </c>
       <c r="B27" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>127405894</v>
       </c>
       <c r="B28" t="n">
-        <v>80159</v>
+        <v>80162</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>127406007</v>
       </c>
       <c r="B29" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>127406344</v>
       </c>
       <c r="B30" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>127406825</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>127406956</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>127406264</v>
       </c>
       <c r="B33" t="n">
-        <v>98454</v>
+        <v>98457</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127095097</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127103007</v>
       </c>
       <c r="B3" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127102976</v>
       </c>
       <c r="B4" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>127103032</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>127102997</v>
       </c>
       <c r="B6" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127102977</v>
       </c>
       <c r="B7" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127103035</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127103002</v>
       </c>
       <c r="B9" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>127102999</v>
       </c>
       <c r="B10" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>127094740</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>127103031</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>127094164</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>127102965</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>127103000</v>
       </c>
       <c r="B15" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         <v>127103008</v>
       </c>
       <c r="B16" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>127102975</v>
       </c>
       <c r="B17" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>127102974</v>
       </c>
       <c r="B18" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>127094909</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>127103001</v>
       </c>
       <c r="B20" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>127103003</v>
       </c>
       <c r="B21" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>127094311</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>127405560</v>
       </c>
       <c r="B23" t="n">
-        <v>92038</v>
+        <v>92046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127406047</v>
       </c>
       <c r="B24" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>127405943</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127406727</v>
+        <v>127405968</v>
       </c>
       <c r="B26" t="n">
-        <v>56858</v>
+        <v>105505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,39 +3079,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591958</v>
+        <v>592050</v>
       </c>
       <c r="R26" t="n">
-        <v>6984415</v>
+        <v>6984433</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3170,10 +3165,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127405968</v>
+        <v>127406727</v>
       </c>
       <c r="B27" t="n">
-        <v>105497</v>
+        <v>56864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3181,34 +3176,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592050</v>
+        <v>591958</v>
       </c>
       <c r="R27" t="n">
-        <v>6984433</v>
+        <v>6984415</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3270,7 +3270,7 @@
         <v>127405894</v>
       </c>
       <c r="B28" t="n">
-        <v>80162</v>
+        <v>80168</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>127406007</v>
       </c>
       <c r="B29" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>127406344</v>
       </c>
       <c r="B30" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406825</v>
+        <v>127406956</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,14 +3589,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591928</v>
+        <v>591868</v>
       </c>
       <c r="R31" t="n">
-        <v>6984491</v>
+        <v>6984472</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406956</v>
+        <v>127406825</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,14 +3686,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591868</v>
+        <v>591928</v>
       </c>
       <c r="R32" t="n">
-        <v>6984472</v>
+        <v>6984491</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>127406264</v>
       </c>
       <c r="B33" t="n">
-        <v>98457</v>
+        <v>98465</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -2770,7 +2770,7 @@
         <v>127405560</v>
       </c>
       <c r="B23" t="n">
-        <v>92046</v>
+        <v>92047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127406047</v>
       </c>
       <c r="B24" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127405968</v>
+        <v>127406727</v>
       </c>
       <c r="B26" t="n">
-        <v>105505</v>
+        <v>56864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,34 +3079,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592050</v>
+        <v>591958</v>
       </c>
       <c r="R26" t="n">
-        <v>6984433</v>
+        <v>6984415</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3165,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127406727</v>
+        <v>127405968</v>
       </c>
       <c r="B27" t="n">
-        <v>56864</v>
+        <v>105506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3176,39 +3181,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591958</v>
+        <v>592050</v>
       </c>
       <c r="R27" t="n">
-        <v>6984415</v>
+        <v>6984433</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3367,7 +3367,7 @@
         <v>127406007</v>
       </c>
       <c r="B29" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>127406344</v>
       </c>
       <c r="B30" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406956</v>
+        <v>127406825</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3589,14 +3589,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591868</v>
+        <v>591928</v>
       </c>
       <c r="R31" t="n">
-        <v>6984472</v>
+        <v>6984491</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,7 +3655,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406825</v>
+        <v>127406956</v>
       </c>
       <c r="B32" t="n">
         <v>79029</v>
@@ -3686,14 +3686,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591928</v>
+        <v>591868</v>
       </c>
       <c r="R32" t="n">
-        <v>6984491</v>
+        <v>6984472</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>127406264</v>
       </c>
       <c r="B33" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -3558,7 +3558,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406825</v>
+        <v>127406956</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3589,14 +3589,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591928</v>
+        <v>591868</v>
       </c>
       <c r="R31" t="n">
-        <v>6984491</v>
+        <v>6984472</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,7 +3655,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406956</v>
+        <v>127406825</v>
       </c>
       <c r="B32" t="n">
         <v>79029</v>
@@ -3686,14 +3686,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591868</v>
+        <v>591928</v>
       </c>
       <c r="R32" t="n">
-        <v>6984472</v>
+        <v>6984491</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -2770,7 +2770,7 @@
         <v>127405560</v>
       </c>
       <c r="B23" t="n">
-        <v>92047</v>
+        <v>92048</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127406047</v>
       </c>
       <c r="B24" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>127405968</v>
       </c>
       <c r="B27" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,32 +3364,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127406007</v>
+        <v>127406825</v>
       </c>
       <c r="B29" t="n">
-        <v>91804</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592065</v>
+        <v>591928</v>
       </c>
       <c r="R29" t="n">
-        <v>6984424</v>
+        <v>6984491</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127406344</v>
+        <v>127406956</v>
       </c>
       <c r="B30" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3472,34 +3472,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592062</v>
+        <v>591868</v>
       </c>
       <c r="R30" t="n">
-        <v>6984382</v>
+        <v>6984472</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3558,45 +3558,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406956</v>
+        <v>127406007</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>91805</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591868</v>
+        <v>592065</v>
       </c>
       <c r="R31" t="n">
-        <v>6984472</v>
+        <v>6984424</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406825</v>
+        <v>127406344</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>91351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591928</v>
+        <v>592062</v>
       </c>
       <c r="R32" t="n">
-        <v>6984491</v>
+        <v>6984382</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>127406264</v>
       </c>
       <c r="B33" t="n">
-        <v>98466</v>
+        <v>98467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -2770,7 +2770,7 @@
         <v>127405560</v>
       </c>
       <c r="B23" t="n">
-        <v>92048</v>
+        <v>92049</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>127406047</v>
       </c>
       <c r="B24" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         <v>127405968</v>
       </c>
       <c r="B27" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,32 +3364,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127406825</v>
+        <v>127406007</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>91806</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591928</v>
+        <v>592065</v>
       </c>
       <c r="R29" t="n">
-        <v>6984491</v>
+        <v>6984424</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127406956</v>
+        <v>127406344</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3472,34 +3472,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591868</v>
+        <v>592062</v>
       </c>
       <c r="R30" t="n">
-        <v>6984472</v>
+        <v>6984382</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3558,45 +3558,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406007</v>
+        <v>127406956</v>
       </c>
       <c r="B31" t="n">
-        <v>91805</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592065</v>
+        <v>591868</v>
       </c>
       <c r="R31" t="n">
-        <v>6984424</v>
+        <v>6984472</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406344</v>
+        <v>127406825</v>
       </c>
       <c r="B32" t="n">
-        <v>91351</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592062</v>
+        <v>591928</v>
       </c>
       <c r="R32" t="n">
-        <v>6984382</v>
+        <v>6984491</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3755,7 +3755,7 @@
         <v>127406264</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127406727</v>
+        <v>127405968</v>
       </c>
       <c r="B26" t="n">
-        <v>56864</v>
+        <v>105508</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,39 +3079,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591958</v>
+        <v>592050</v>
       </c>
       <c r="R26" t="n">
-        <v>6984415</v>
+        <v>6984433</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3170,10 +3165,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127405968</v>
+        <v>127406727</v>
       </c>
       <c r="B27" t="n">
-        <v>105508</v>
+        <v>56864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3181,34 +3176,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592050</v>
+        <v>591958</v>
       </c>
       <c r="R27" t="n">
-        <v>6984433</v>
+        <v>6984415</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3364,32 +3364,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127406007</v>
+        <v>127406825</v>
       </c>
       <c r="B29" t="n">
-        <v>91806</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592065</v>
+        <v>591928</v>
       </c>
       <c r="R29" t="n">
-        <v>6984424</v>
+        <v>6984491</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127406344</v>
+        <v>127406956</v>
       </c>
       <c r="B30" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3472,34 +3472,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
+          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592062</v>
+        <v>591868</v>
       </c>
       <c r="R30" t="n">
-        <v>6984382</v>
+        <v>6984472</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3558,45 +3558,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127406956</v>
+        <v>127406007</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>91806</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
+          <t>Gullabborrtjärnen, Gullabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591868</v>
+        <v>592065</v>
       </c>
       <c r="R31" t="n">
-        <v>6984472</v>
+        <v>6984424</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127406825</v>
+        <v>127406344</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591928</v>
+        <v>592062</v>
       </c>
       <c r="R32" t="n">
-        <v>6984491</v>
+        <v>6984382</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3852,6 +3852,610 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129431280</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>592053</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6984426</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129431278</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>591898</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6984537</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129431309</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80184</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>592018</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6984416</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129431310</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>592018</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6984416</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129431308</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>591975</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6984412</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129431311</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91996</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>592072</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6984426</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -4061,7 +4061,7 @@
         <v>129431309</v>
       </c>
       <c r="B36" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>129431310</v>
       </c>
       <c r="B37" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>129431311</v>
       </c>
       <c r="B39" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -4364,7 +4364,7 @@
         <v>129431311</v>
       </c>
       <c r="B39" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -4364,7 +4364,7 @@
         <v>129431311</v>
       </c>
       <c r="B39" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -3854,7 +3854,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129431280</v>
+        <v>129431278</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592053</v>
+        <v>591898</v>
       </c>
       <c r="R34" t="n">
-        <v>6984426</v>
+        <v>6984537</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3956,7 +3956,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129431278</v>
+        <v>129431280</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>591898</v>
+        <v>592053</v>
       </c>
       <c r="R35" t="n">
-        <v>6984537</v>
+        <v>6984426</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -4364,7 +4364,7 @@
         <v>129431311</v>
       </c>
       <c r="B39" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -3854,7 +3854,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129431278</v>
+        <v>129431280</v>
       </c>
       <c r="B34" t="n">
         <v>57727</v>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591898</v>
+        <v>592053</v>
       </c>
       <c r="R34" t="n">
-        <v>6984537</v>
+        <v>6984426</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3956,7 +3956,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129431280</v>
+        <v>129431278</v>
       </c>
       <c r="B35" t="n">
         <v>57727</v>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592053</v>
+        <v>591898</v>
       </c>
       <c r="R35" t="n">
-        <v>6984426</v>
+        <v>6984537</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>

--- a/artfynd/A 21213-2025 artfynd.xlsx
+++ b/artfynd/A 21213-2025 artfynd.xlsx
@@ -3854,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129431278</v>
+        <v>129431280</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591898</v>
+        <v>592053</v>
       </c>
       <c r="R34" t="n">
-        <v>6984537</v>
+        <v>6984426</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3956,10 +3956,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129431280</v>
+        <v>129431278</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592053</v>
+        <v>591898</v>
       </c>
       <c r="R35" t="n">
-        <v>6984426</v>
+        <v>6984537</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4061,7 +4061,7 @@
         <v>129431309</v>
       </c>
       <c r="B36" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>129431310</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>129431308</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>129431311</v>
       </c>
       <c r="B39" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
